--- a/XlsxSharp.Tests/Resource/Examples/Misc/Collections.xlsx
+++ b/XlsxSharp.Tests/Resource/Examples/Misc/Collections.xlsx
@@ -1,89 +1,89 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Collections" sheetId="1" r:id="rId2"/>
-  </x:sheets>
-  <x:definedNames>
-    <x:definedName name="Titles">Collections!$A$1:$A$1,Collections!$C$1:$H$1,Collections!$A$6:$D$6,Collections!$F$6:$H$6</x:definedName>
-  </x:definedNames>
-  <x:calcPr calcId="125725"/>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet r:id="rId1" name="Collections" sheetId="1"/>
+  </sheets>
+  <definedNames>
+    <definedName name="Titles">Collections!$A$1:$A$1,Collections!$C$1:$H$1,Collections!$A$6:$D$6,Collections!$F$6:$H$6</definedName>
+  </definedNames>
+  <calcPr calcId="125725"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>Strings</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arrays</x:t>
-  </x:si>
-  <x:si>
-    <x:t>House</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Car</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DataTable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Query</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Indocin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>David</x:t>
-  </x:si>
-  <x:si>
-    <x:t>John</x:t>
-  </x:si>
-  <x:si>
-    <x:t>On Elm St.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Enebrel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sam</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Luis</x:t>
-  </x:si>
-  <x:si>
-    <x:t>On 23rd St.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hydralazine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Christoff</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Henry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>On 5th Ave.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Combivent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Janet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dilantin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Melanie</x:t>
-  </x:si>
-</x:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t>Strings</t>
+  </si>
+  <si>
+    <t>Arrays</t>
+  </si>
+  <si>
+    <t>House</t>
+  </si>
+  <si>
+    <t>Car</t>
+  </si>
+  <si>
+    <t>DataTable</t>
+  </si>
+  <si>
+    <t>Query</t>
+  </si>
+  <si>
+    <t>Indocin</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>On Elm St.</t>
+  </si>
+  <si>
+    <t>Enebrel</t>
+  </si>
+  <si>
+    <t>Sam</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>On 23rd St.</t>
+  </si>
+  <si>
+    <t>Hydralazine</t>
+  </si>
+  <si>
+    <t>Christoff</t>
+  </si>
+  <si>
+    <t>Henry</t>
+  </si>
+  <si>
+    <t>On 5th Ave.</t>
+  </si>
+  <si>
+    <t>Combivent</t>
+  </si>
+  <si>
+    <t>Janet</t>
+  </si>
+  <si>
+    <t>Dilantin</t>
+  </si>
+  <si>
+    <t>Melanie</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -435,198 +435,198 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:H11"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="6.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11.282054" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="8.567768" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.996339" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="1.710625" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="6.139196" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11.282054" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="2.996339" style="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:8">
-      <x:c r="A1" s="2" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D1" s="2"/>
-      <x:c r="E1" s="2"/>
-      <x:c r="F1" s="2"/>
-      <x:c r="G1" s="2"/>
-      <x:c r="H1" s="2"/>
-    </x:row>
-    <x:row r="2" spans="1:8">
-      <x:c r="A2" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E2" s="0">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8">
-      <x:c r="A3" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:8">
-      <x:c r="C4" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E4" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F4" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G4" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H4" s="0">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:8">
-      <x:c r="A6" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B6" s="2"/>
-      <x:c r="C6" s="2"/>
-      <x:c r="D6" s="2"/>
-      <x:c r="F6" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G6" s="2"/>
-      <x:c r="H6" s="2"/>
-    </x:row>
-    <x:row r="7" spans="1:8">
-      <x:c r="A7" s="0">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="1">
-        <x:v>36526</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H7" s="0">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:8">
-      <x:c r="A8" s="0">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="1">
-        <x:v>36527</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="H8" s="0">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:8">
-      <x:c r="A9" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D9" s="1">
-        <x:v>36528</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="0">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:8">
-      <x:c r="A10" s="0">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D10" s="1">
-        <x:v>36529</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:8">
-      <x:c r="A11" s="0">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D11" s="1">
-        <x:v>36530</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells count="3">
-    <x:mergeCell ref="C1:H1"/>
-    <x:mergeCell ref="A6:D6"/>
-    <x:mergeCell ref="F6:H6"/>
-  </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" style="0" customWidth="1" width="6.853482"/>
+    <col min="2" max="2" style="0" customWidth="1" width="11.282054"/>
+    <col min="3" max="3" style="0" customWidth="1" width="8.567768"/>
+    <col min="4" max="4" style="0" customWidth="1" width="8.996339"/>
+    <col min="5" max="5" style="0" customWidth="1" width="1.710625"/>
+    <col min="6" max="6" style="0" customWidth="1" width="6.139196"/>
+    <col min="7" max="7" style="0" customWidth="1" width="11.282054"/>
+    <col min="8" max="8" style="0" customWidth="1" width="2.996339"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="0">
+        <v>1</v>
+      </c>
+      <c r="D2" s="0">
+        <v>2</v>
+      </c>
+      <c r="E2" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="C4" s="0">
+        <v>1</v>
+      </c>
+      <c r="D4" s="0">
+        <v>2</v>
+      </c>
+      <c r="E4" s="0">
+        <v>3</v>
+      </c>
+      <c r="F4" s="0">
+        <v>4</v>
+      </c>
+      <c r="G4" s="0">
+        <v>5</v>
+      </c>
+      <c r="H4" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="0">
+        <v>25</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1">
+        <v>36526</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="0">
+        <v>50</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="1">
+        <v>36527</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="0">
+        <v>10</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1">
+        <v>36528</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="0">
+        <v>21</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1">
+        <v>36529</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="0">
+        <v>100</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="1">
+        <v>36530</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="F6:H6"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>